--- a/rules/CORE-000158/negative/02/data/unit-test-coreid-CG0163-negative-2.xlsx
+++ b/rules/CORE-000158/negative/02/data/unit-test-coreid-CG0163-negative-2.xlsx
@@ -538,7 +538,7 @@
       <c r="E2" s="4" t="str">
         <v>IDVAR</v>
       </c>
-      <c r="F2" s="2" t="str">
+      <c r="F2" s="4" t="str">
         <v>[ABSENT]</v>
       </c>
     </row>
